--- a/CI_Interface_Register_Template.xlsx
+++ b/CI_Interface_Register_Template.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interface Register'!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interface Register'!$A$1:$S$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -562,31 +562,45 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>•  Variant Applicability identifies which PN variant(s) of a CI each interface row applies to, per [XXX-CM-GUIDE-001] §4.2 and §6: enter 'All', specific variant PIN(s), or 'N/A'. Where one ICD carries distinct callouts for different variants, use one row per distinct interface definition — appearing on the same ICD is not evidence of a common interface.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>•  For separate-CI verdicts from [XXX-CM-GUIDE-001], verify every pairwise boundary between the new sibling CIs appears here or carries a signed no-interface determination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Column notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>•  Boundary Type: Internal (CI-to-CI within the system), External (system to external system/facility/support equipment), or Control-Level (Acquirer-controlled to Supplier-controlled boundary).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>•  Controlling Baseline: which baseline the interface requirements belong to via the specification that invokes them (FBL for system-boundary interfaces via the system spec; ABL for CI-to-CI interfaces via item specs). Changes to baselined interfaces are processed through formal change action (Floor ID F37).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>•  Boundary Type: Internal (CI-to-CI within the system), External (system to external system/facility/support equipment), or Control-Level (Acquirer-controlled to Supplier-controlled boundary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>•  Controlling Baseline: which baseline the interface requirements belong to via the specification that invokes them (FBL for system-boundary interfaces via the system spec; ABL for CI-to-CI interfaces via item specs). Changes to baselined interfaces are processed through formal change action (Floor ID F37).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>•  Control Authority: the CCB controlling the defining documentation, and/or ICWG where the Acquirer operates one (Floor ID F38).</t>
         </is>
@@ -603,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -619,11 +633,12 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,25 +709,30 @@
       </c>
       <c r="N1" s="4" t="inlineStr">
         <is>
+          <t>Variant Applicability</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
           <t>Safety-Related (Y/N)</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Hazard Control Ref</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Coverage Check Result</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Coverage Check Date</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -778,21 +798,26 @@
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr">
         <is>
           <t>System-boundary data link; ICWG rep per PROC-001 §5.5.3</t>
         </is>
@@ -858,25 +883,30 @@
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>HL-015-C2</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>FCC/OFP execution interface; hosts hazard control</t>
         </is>
@@ -942,44 +972,49 @@
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
+          <t>ACT-2230-002 only</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>HL-014-C1</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>Command/monitor loop to elevator actuator</t>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Baseline-connector variant; see IF-0006 for -004 variant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IF-0004</t>
+          <t>IF-0006</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Control-Level</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>CI-0012</t>
+          <t>CI-0013</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -996,7 +1031,7 @@
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>PS-2230 §3.3 (interface section)</t>
+          <t>ICD-2200-210 §4.2 (distinct callout)</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1021,118 +1056,197 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>if.FCS-ACT</t>
+          <t>if.FCC-ACT2</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr"/>
+          <t>ACT-2230-004 only</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
+          <t>HL-014-C1</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
           <t>Covered</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>Acquirer/Supplier control boundary; flowdown per SSOW-114</t>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>Revised-connector variant; distinct callout on same ICD per GUIDE-001 §4.2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>IF-0004</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Control-Level</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CI-0012</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CI-0021</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>PS-2230 §3.3 (interface section)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Program CCB</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>if.FCS-ACT</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>Acquirer/Supplier control boundary; flowdown per SSOW-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>IF-0005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>CI-0014</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>CI-0021</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>No-Interface</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>J. Ramirez, SE Lead</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>No direct OFP-to-actuator interface; all traffic via FCC (IF-0002/0003)</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -1153,6 +1267,7 @@
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -1173,6 +1288,7 @@
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -1193,6 +1309,7 @@
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>
+      <c r="S10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -1213,6 +1330,7 @@
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -1233,6 +1351,7 @@
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
+      <c r="S12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -1253,6 +1372,7 @@
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -1273,6 +1393,7 @@
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>
+      <c r="S14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -1293,6 +1414,7 @@
       <c r="P15" s="6" t="n"/>
       <c r="Q15" s="6" t="n"/>
       <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -1313,6 +1435,7 @@
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
       <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -1333,6 +1456,7 @@
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
       <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -1353,6 +1477,7 @@
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n"/>
       <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -1373,6 +1498,7 @@
       <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
       <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1393,6 +1519,7 @@
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n"/>
       <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1413,6 +1540,7 @@
       <c r="P21" s="6" t="n"/>
       <c r="Q21" s="6" t="n"/>
       <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1433,6 +1561,7 @@
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n"/>
       <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1453,6 +1582,7 @@
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
       <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1473,6 +1603,7 @@
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n"/>
       <c r="R24" s="6" t="n"/>
+      <c r="S24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1493,6 +1624,7 @@
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="6" t="n"/>
       <c r="R25" s="6" t="n"/>
+      <c r="S25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1513,6 +1645,7 @@
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n"/>
       <c r="R26" s="6" t="n"/>
+      <c r="S26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1533,6 +1666,7 @@
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
       <c r="R27" s="6" t="n"/>
+      <c r="S27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1553,6 +1687,7 @@
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n"/>
       <c r="R28" s="6" t="n"/>
+      <c r="S28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1573,6 +1708,7 @@
       <c r="P29" s="6" t="n"/>
       <c r="Q29" s="6" t="n"/>
       <c r="R29" s="6" t="n"/>
+      <c r="S29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -1593,6 +1729,7 @@
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n"/>
       <c r="R30" s="6" t="n"/>
+      <c r="S30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1613,6 +1750,7 @@
       <c r="P31" s="6" t="n"/>
       <c r="Q31" s="6" t="n"/>
       <c r="R31" s="6" t="n"/>
+      <c r="S31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1633,6 +1771,7 @@
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n"/>
       <c r="R32" s="6" t="n"/>
+      <c r="S32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1653,6 +1792,7 @@
       <c r="P33" s="6" t="n"/>
       <c r="Q33" s="6" t="n"/>
       <c r="R33" s="6" t="n"/>
+      <c r="S33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1673,6 +1813,7 @@
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="n"/>
       <c r="R34" s="6" t="n"/>
+      <c r="S34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1693,6 +1834,7 @@
       <c r="P35" s="6" t="n"/>
       <c r="Q35" s="6" t="n"/>
       <c r="R35" s="6" t="n"/>
+      <c r="S35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1713,9 +1855,31 @@
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n"/>
       <c r="R36" s="6" t="n"/>
+      <c r="S36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="n"/>
+      <c r="Q37" s="6" t="n"/>
+      <c r="R37" s="6" t="n"/>
+      <c r="S37" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1"/>
+  <autoFilter ref="A1:S1"/>
   <dataValidations count="7">
     <dataValidation sqref="B2:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Select a value from the list (see Lists sheet)." type="list">
       <formula1>=Lists!$A$2:$A$4</formula1>
@@ -1732,10 +1896,10 @@
     <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Select a value from the list (see Lists sheet)." type="list">
       <formula1>=Lists!$E$2:$E$3</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Select a value from the list (see Lists sheet)." type="list">
+    <dataValidation sqref="O2:O200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Select a value from the list (see Lists sheet)." type="list">
       <formula1>=Lists!$E$2:$E$3</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Select a value from the list (see Lists sheet)." type="list">
+    <dataValidation sqref="Q2:Q200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Select a value from the list (see Lists sheet)." type="list">
       <formula1>=Lists!$F$2:$F$4</formula1>
     </dataValidation>
   </dataValidations>
